--- a/dati/Riga-SECAP-vidusposms-dati.xlsx
+++ b/dati/Riga-SECAP-vidusposms-dati.xlsx
@@ -442,14 +442,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rīgas SECAP 2022–2030 vidusposma pārskats – atvērtie dati (darba versija)</t>
+          <t>Rīgas SECAP 2022–2030 vidusposma pārskats – atvērtie dati</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sagatavots: 2026-10-21</t>
+          <t>Sagatavots: 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -477,14 +477,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Procentu rādītāji norādīti procentos (piem. 46,85 = 46,85 %).</t>
+          <t>Procentu rādītāji norādīti procentos (piem. 45,5 = 45,5 %).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pasākumu statuss ir darba versija. Plānotā ietekme – no SECAP2030 pasākumu tabulas.</t>
+          <t>Pasākumu statuss – 2025. gada novērtējums. Plānotā ietekme – no SECAP2030 pasākumu tabulas.</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1029,7 +1029,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Kumulatīvais pašvaldības ēku skaits, kurās veikta energoefektivitātes atjaunošana. ĪD dati; 2020–2025 dati nav pieejami.</t>
+          <t>Kumulatīvais pašvaldības ēku skaits, kurās veikta energoefektivitātes atjaunošana. ĪD dati; 2020–2025 dati nav apkopoti.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Rīgas Siltums dati</t>
+          <t>AS “Rīgas siltums” dati</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="G32" t="n">
         <v>33.38</v>
@@ -2154,12 +2154,12 @@
         <v>41.74</v>
       </c>
       <c r="K32" t="n">
-        <v>46.85</v>
+        <v>45.5</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Rīgas Siltums dati</t>
+          <t>AS “Rīgas siltums” dati</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dabasgāzes patēriņš mājokļu sektorā (mājsaimniecības)</t>
+          <t>Zudumi siltumtīklos aktīvajā apkures sezonā (oktobris–aprīlis)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2182,36 +2182,21 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Decentralizētā energoapgāde</t>
+          <t>Siltumapgāde</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GWh/gadā</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>294.7</v>
-      </c>
-      <c r="G33" t="n">
-        <v>518.7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>438.352</v>
-      </c>
-      <c r="I33" t="n">
-        <v>424.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>420</v>
+          <t>%</t>
+        </is>
       </c>
       <c r="K33" t="n">
-        <v>415.877</v>
+        <v>9.77</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Gaso dati</t>
+          <t>Datus sniedz AS “Rīgas siltums”. Relatīvie siltumenerģijas zudumi Rīgas pilsētas CSS siltumtīklos aktīvajā apkures sezonā (oktobris–aprīlis), % no tīklā nodotās siltumenerģijas; vērtība par finanšu gadu (2025 = 2024./2025. finanšu gads). Rādītājs ieviests vidusposmā atbilstoši NEKP2030 pasākuma 3.1.3.11 rezultatīvajam rādītājam (siltuma zudumu īpatsvars apkures sezonā &lt; 10 % līdz 2030. gadam), kas iekļauts arī Rīgas valstspilsētas CSS attīstības stratēģijas 2026.–2040. gadam konceptuālajā ziņojumā; tas aizstāj SECAP2030 rādītāju “Relatīvie siltumenerģijas zudumi siltumtīklos” (gada zudumi, bāze 11,77 %). Zudumus būtiski ietekmē laikapstākļi (āra temperatūra, apkures sezonas ilgums). Gada zudumi: 2024./2025. FG – 12,49 %; 2025./2026. FG – 11,8 % (apkures sezonā 9,30 %).</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2224,7 +2209,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dabasgāzes patēriņš sabiedriskais sektors (pārējie lietotāji)</t>
+          <t>Dabasgāzes patēriņš mājokļu sektorā (mājsaimniecības)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2243,22 +2228,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3167</v>
+        <v>294.7</v>
       </c>
       <c r="G34" t="n">
-        <v>3096</v>
+        <v>518.7</v>
       </c>
       <c r="H34" t="n">
-        <v>2077</v>
+        <v>438.352</v>
       </c>
       <c r="I34" t="n">
-        <v>2195</v>
+        <v>424.4</v>
       </c>
       <c r="J34" t="n">
-        <v>2429</v>
+        <v>420</v>
       </c>
       <c r="K34" t="n">
-        <v>2101</v>
+        <v>415.877</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
@@ -2276,7 +2261,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dabasgāzes patēriņš Rīgā kopā</t>
+          <t>Dabasgāzes patēriņš sabiedriskais sektors (pārējie lietotāji)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2286,7 +2271,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dabasgāze</t>
+          <t>Decentralizētā energoapgāde</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2295,22 +2280,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3461</v>
+        <v>3167</v>
       </c>
       <c r="G35" t="n">
-        <v>3614</v>
+        <v>3096</v>
       </c>
       <c r="H35" t="n">
-        <v>2515</v>
+        <v>2077</v>
       </c>
       <c r="I35" t="n">
-        <v>2619</v>
+        <v>2195</v>
       </c>
       <c r="J35" t="n">
-        <v>2849</v>
+        <v>2429</v>
       </c>
       <c r="K35" t="n">
-        <v>2516.877</v>
+        <v>2101</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
@@ -2328,7 +2313,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Decentralizētās siltumapgādes īpatsvars siltumenerģijas galapatēriņā</t>
+          <t>Dabasgāzes patēriņš Rīgā kopā</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2338,36 +2323,36 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Decentralizētā energoapgāde</t>
+          <t>Dabasgāze</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh/gadā</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>49.87</v>
+        <v>3461</v>
       </c>
       <c r="G36" t="n">
-        <v>45.94</v>
+        <v>3614</v>
       </c>
       <c r="H36" t="n">
-        <v>46.32</v>
+        <v>2515</v>
       </c>
       <c r="I36" t="n">
-        <v>44.58</v>
+        <v>2619</v>
       </c>
       <c r="J36" t="n">
-        <v>46.1</v>
+        <v>2849</v>
       </c>
       <c r="K36" t="n">
-        <v>42.72</v>
+        <v>2516.877</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>SEG inventarizācija (Riga-CO2-Kopa-2025): decentralizētā kurināmā patēriņš / kopējais siltumenerģijas galapatēriņš (CSS + decentralizētā), Kopā_2025 rinda 67 / rinda 24. Ietver ETS iekārtas un GASO “pārējos” patērētājus.</t>
+          <t>Gaso dati</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2380,7 +2365,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AER īpatsvars decentralizētajā siltumapgādē</t>
+          <t>Decentralizētās siltumapgādes īpatsvars siltumenerģijas galapatēriņā</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2399,27 +2384,27 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>41.82</v>
+        <v>49.87</v>
       </c>
       <c r="G37" t="n">
-        <v>34.63</v>
+        <v>45.94</v>
       </c>
       <c r="H37" t="n">
-        <v>42.6</v>
+        <v>46.32</v>
       </c>
       <c r="I37" t="n">
-        <v>34.18</v>
+        <v>44.58</v>
       </c>
       <c r="J37" t="n">
-        <v>38.4</v>
+        <v>46.1</v>
       </c>
       <c r="K37" t="n">
-        <v>34.23</v>
+        <v>42.72</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>SEG inventarizācija (Riga-CO2-Kopa-2025): (biomasa decentralizētajā apgādē pēc CSS atskaitīšanas, Decentralizēti_2020–2025 lapas + mājsaimniecību AER ārpus CSS) / decentralizētā kurināmā patēriņš (Kopā_2025 rinda 67). Mājsaimniecību AER = rinda 17 − dabasgāze (GASO).</t>
+          <t>Avots: Rīgas SEG inventarizācija (REA, Riga-CO2-monitorings-2020-2025.xlsx, lapa Kopā_2025). Aprēķins: decentralizētā kurināmā patēriņš (rinda 67) / (CSS patērētājiem nodotā siltumenerģija (rinda 65) + decentralizētā kurināmā patēriņš). Decentralizētais kurināmā patēriņš ietver: (1) dabasgāzi ārpus CSS – AS “Gaso” dati par pārējo lietotāju patēriņu, atskaitot CSS siltumražošanā izmantoto dabasgāzi; (2) pārējo kurināmo (koksne, šķelda, granulas, sašķidrinātā gāze, dīzeļdegviela, mazuts, biogāze) – LVĢMC datubāze “2-Gaiss” par sadedzināšanas iekārtām Rīgā, t. sk. ETS uzņēmumi un tehnoloģiskajos procesos izmantotais kurināmais, atskaitot CSS izmantoto biomasu; (3) CSS nepieslēgtās mājsaimniecības – aprēķins (104,4 kWh/m² × 6,52 milj. m² CSS nepieslēgtā dzīvojamā fonda; dabasgāzes patēriņš – AS “Gaso” dati). CSS siltumenerģija – AS “Rīgas siltums” dati (rādītājs 3001). Ierobežojumi: skaitītājā ir kurināmā patēriņš, bet saucējā – CSS nodotā siltumenerģija; pārrēķinot kurināmo siltumenerģijā (92 % lietderība), 2025. gada īpatsvars būtu ~41 %. Mājsaimniecību daļa ir modelēta un gadu gaitā maz mainās, tāpēc izmaiņas galvenokārt nosaka pakalpojumu un rūpniecības kurināmā patēriņš. CSS attīstības stratēģijā (pēc apsildāmās platības un īpatnējā patēriņa) īpatsvars aplēsts ~47 %. SECAP2030 bāzi 44 % (2019) ar šiem datiem nevar atkārtot.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2432,7 +2417,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kopējais elektroenerģijas patēriņš</t>
+          <t>AER īpatsvars decentralizētajā siltumapgādē</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2442,36 +2427,36 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Elektroenerģija</t>
+          <t>Decentralizētā energoapgāde</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GWh/gadā</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1960.311</v>
+        <v>41.82</v>
       </c>
       <c r="G38" t="n">
-        <v>1956.8614</v>
+        <v>34.63</v>
       </c>
       <c r="H38" t="n">
-        <v>1921.0319</v>
+        <v>42.6</v>
       </c>
       <c r="I38" t="n">
-        <v>1840.3876</v>
+        <v>34.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1937.0865</v>
+        <v>38.4</v>
       </c>
       <c r="K38" t="n">
-        <v>1970.4334</v>
+        <v>34.23</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Sadales tīkls dati. Bez transporta elektroenerģijas, kas uzskaitīta transporta sektorā (rādītājs 4011) – kā SEG inventarizācijā (Kopā_2025 rinda 66).</t>
+          <t>Avots: Rīgas SEG inventarizācija (REA, Riga-CO2-monitorings-2020-2025.xlsx, lapas Decentralizēti_2020–2025 un Kopā_2025). Aprēķins: AER kurināmā patēriņš decentralizētajā siltumapgādē / decentralizētā kurināmā patēriņš (Kopā_2025 rinda 67, tas pats saucējs kā rādītājam 3007). AER patēriņš ietver: (1) biomasu (koksne, šķelda, granulas, malka, biogāze) sadedzināšanas iekārtās Rīgā – LVĢMC datubāze “2-Gaiss”, t. sk. ETS uzņēmumi un tehnoloģiskajos procesos izmantotā koksne, atskaitot CSS siltumražošanā izmantoto biomasu; (2) AER CSS nepieslēgtajās mājsaimniecībās – atlikums: modelētais mājsaimniecību siltumenerģijas patēriņš (104,4 kWh/m² × 6,52 milj. m² CSS nepieslēgtā dzīvojamā fonda; Kopā_2025 rinda 17) mīnus AS “Gaso” dati par mājsaimniecību dabasgāzes patēriņu. 2025. gadā: biomasa 454 GWh + mājsaimniecību AER 265 GWh = 719 GWh no 2 102 GWh (34,2 %). Ierobežojumi: gada vērtības svārstās (34–43 %), jo rezultātu būtiski ietekmē CSS izmantotās biomasas atskaitīšana un dažu lielu rūpniecības uzņēmumu koksnes patēriņš; mājsaimniecību AER ir aprēķināts kā atlikums, tāpēc dabasgāzes patēriņa izmaiņas to automātiski ietekmē pretējā virzienā (piem., 2020. gadā mājsaimniecību dabasgāzes patēriņš bija neparasti zems). SECAP2030 bāzi 42 % (2019) ar šiem datiem nevar atkārtot; progress mērīts pret 2020. gada vērtību.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2484,7 +2469,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>No AER saražotās elektroenerģijas īpatsvars</t>
+          <t>Kopējais elektroenerģijas patēriņš</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2499,38 +2484,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>GWh/gadā</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.1</v>
+        <v>1960.311</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1956.8614</v>
       </c>
       <c r="H39" t="n">
-        <v>5.2</v>
+        <v>1921.0319</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>1840.3876</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>1937.0865</v>
       </c>
       <c r="K39" t="n">
-        <v>6.7</v>
+        <v>1970.4334</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Centrālā statistikas pārvalde, rādītājs</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>https://data.stat.gov.lv/pxweb/lv/OSP_PUB/START__NOZ__EN__ENB/ENB210</t>
-        </is>
-      </c>
+          <t>Sadales tīkls dati. Bez transporta elektroenerģijas, kas uzskaitīta transporta sektorā (rādītājs 4011) – kā SEG inventarizācijā (Kopā_2025 rinda 66).</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2540,7 +2521,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Saules elektroenerģijas apjoms, kas nodots tīklā (juridiskas personas)</t>
+          <t>No AER saražotās elektroenerģijas īpatsvars</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2555,26 +2536,26 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GWh/gadā</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.633</v>
+        <v>3.1</v>
       </c>
       <c r="G40" t="n">
-        <v>1.094</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>4.249</v>
+        <v>5.2</v>
       </c>
       <c r="I40" t="n">
-        <v>19.703</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>44.226</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>70.57299999999999</v>
+        <v>6.7</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
@@ -2584,7 +2565,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://data.stat.gov.lv/pxweb/lv/OSP_PUB/START__NOZ__EN__ENA/ENA050</t>
+          <t>https://data.stat.gov.lv/pxweb/lv/OSP_PUB/START__NOZ__EN__ENB/ENB210</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2577,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Energokopienu skaits Rīgā</t>
+          <t>Saules elektroenerģijas apjoms, kas nodots tīklā (juridiskas personas)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2606,41 +2587,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Energokopienas</t>
+          <t>Elektroenerģija</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>skaits</t>
+          <t>GWh/gadā</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>4.249</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>19.703</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>44.226</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>70.57299999999999</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Valsts Vides dienesta dati, atvērto datu portāls, konsultācijas</t>
+          <t>Centrālā statistikas pārvalde, rādītājs</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://data.gov.lv/dati/eng/dataset/vvdenergokopienas/resource/e0b8ed6d-139d-404f-974a-fbf3375f6377</t>
+          <t>https://data.stat.gov.lv/pxweb/lv/OSP_PUB/START__NOZ__EN__ENA/ENA050</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2633,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CO2 emisijas - centralizētā siltumapgāde</t>
+          <t>Energokopienu skaits Rīgā</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2662,39 +2643,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CO2 emisijas</t>
+          <t>Energokopienas</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>tCO2/gadā</t>
+          <t>skaits</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>399620</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>473444.543</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>404112.4552</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>359236.7792</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>363595.185</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>338502.4349</v>
+        <v>1</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>CSS patērētājiem nodotās siltumenerģijas (rādītājs 3001) CO2 emisijas – kurināmā patēriņš reiz emisiju faktori. SEG inventarizācija.</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>Valsts Vides dienesta dati, atvērto datu portāls, konsultācijas</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://data.gov.lv/dati/eng/dataset/vvdenergokopienas/resource/e0b8ed6d-139d-404f-974a-fbf3375f6377</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2704,7 +2689,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CO2 emisijas - elektroenerģijas patēriņš</t>
+          <t>CO2 emisijas - centralizētā siltumapgāde</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2723,27 +2708,27 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>213674</v>
+        <v>399620</v>
       </c>
       <c r="G43" t="n">
-        <v>213298</v>
+        <v>473444.543</v>
       </c>
       <c r="H43" t="n">
-        <v>209391</v>
+        <v>404112.4552</v>
       </c>
       <c r="I43" t="n">
-        <v>200602</v>
+        <v>359236.7792</v>
       </c>
       <c r="J43" t="n">
-        <v>211141</v>
+        <v>363595.185</v>
       </c>
       <c r="K43" t="n">
-        <v>214777</v>
+        <v>338502.4349</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Kopējā elektroenerģijas patēriņa (rādītājs 3008) CO2 emisijas – patēriņš reiz elektroenerģijas emisiju faktors. Atbilst summai 1016 + 1018 + 1019 + 2008 + 3016. SEG inventarizācija.</t>
+          <t>CSS patērētājiem nodotās siltumenerģijas (rādītājs 3001) CO2 emisijas – kurināmā patēriņš reiz emisiju faktori. SEG inventarizācija.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -2756,7 +2741,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CO2 emisijas - kurināmā patēriņš</t>
+          <t>CO2 emisijas - elektroenerģijas patēriņš</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2775,27 +2760,27 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>297817</v>
+        <v>213674</v>
       </c>
       <c r="G44" t="n">
-        <v>355019</v>
+        <v>213298</v>
       </c>
       <c r="H44" t="n">
-        <v>282637.0732</v>
+        <v>209391</v>
       </c>
       <c r="I44" t="n">
-        <v>288432.3481</v>
+        <v>200602</v>
       </c>
       <c r="J44" t="n">
-        <v>278340.4046</v>
+        <v>211141</v>
       </c>
       <c r="K44" t="n">
-        <v>262975.4072</v>
+        <v>214777</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Decentralizētās siltumapgādes kurināmā (ārpus CSS) patēriņa CO2 emisijas – kurināmā patēriņš reiz emisiju faktori. SEG inventarizācija.</t>
+          <t>Kopējā elektroenerģijas patēriņa (rādītājs 3008) CO2 emisijas – patēriņš reiz elektroenerģijas emisiju faktors. Atbilst summai 1016 + 1018 + 1019 + 2008 + 3016. SEG inventarizācija.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -2808,7 +2793,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CO2 emisijas - pakalpojumu un rūpniecības sektors, pārējie (siltumenerģija un kurināmais)</t>
+          <t>CO2 emisijas - kurināmā patēriņš</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2827,27 +2812,27 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>305940</v>
+        <v>297817</v>
       </c>
       <c r="G45" t="n">
-        <v>333818</v>
+        <v>355019</v>
       </c>
       <c r="H45" t="n">
-        <v>265389</v>
+        <v>282637.0732</v>
       </c>
       <c r="I45" t="n">
-        <v>271775.77</v>
+        <v>288432.3481</v>
       </c>
       <c r="J45" t="n">
-        <v>259767</v>
+        <v>278340.4046</v>
       </c>
       <c r="K45" t="n">
-        <v>240398</v>
+        <v>262975.4072</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Pakalpojumu, rūpniecības un pārējo patērētāju CO2 emisijas no siltumenerģijas (CSS) un kurināmā. SEG aprēķinu tabula – dalījums patēriņa gala sektoros; 1017 + 2007 + 3015 = 3012 + 3014.</t>
+          <t>Decentralizētās siltumapgādes kurināmā (ārpus CSS) patēriņa CO2 emisijas – kurināmā patēriņš reiz emisiju faktori. SEG inventarizācija.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -2860,7 +2845,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CO2 emisijas - pakalpojumi, rūpniecība un pārējie, t. sk. lauksaimniecība (elektroenerģija)</t>
+          <t>CO2 emisijas - pakalpojumu un rūpniecības sektors, pārējie (siltumenerģija un kurināmais)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2879,27 +2864,27 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>148102</v>
+        <v>305940</v>
       </c>
       <c r="G46" t="n">
-        <v>146360</v>
+        <v>333818</v>
       </c>
       <c r="H46" t="n">
-        <v>145774</v>
+        <v>265389</v>
       </c>
       <c r="I46" t="n">
-        <v>139239</v>
+        <v>271775.77</v>
       </c>
       <c r="J46" t="n">
-        <v>148417</v>
+        <v>259767</v>
       </c>
       <c r="K46" t="n">
-        <v>150566</v>
+        <v>240398</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Pakalpojumu, rūpniecības un pārējo patērētāju (t. sk. lauksaimniecības) elektroenerģijas patēriņa CO2 emisijas. SEG aprēķinu tabula – dalījums patēriņa gala sektoros.</t>
+          <t>Pakalpojumu, rūpniecības un pārējo patērētāju CO2 emisijas no siltumenerģijas (CSS) un kurināmā. SEG aprēķinu tabula – dalījums patēriņa gala sektoros; 1017 + 2007 + 3015 = 3012 + 3014.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -2907,51 +2892,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Reģistrētie transportlīdzekļi, kopā</t>
+          <t>CO2 emisijas - pakalpojumi, rūpniecība un pārējie, t. sk. lauksaimniecība (elektroenerģija)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Transports</t>
+          <t>Enerģija</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Transports, kopā</t>
+          <t>CO2 emisijas</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>skaits</t>
+          <t>tCO2/gadā</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>283627</v>
+        <v>148102</v>
       </c>
       <c r="G47" t="n">
-        <v>288527.8874</v>
+        <v>146360</v>
       </c>
       <c r="H47" t="n">
-        <v>290614.7807</v>
+        <v>145774</v>
       </c>
       <c r="I47" t="n">
-        <v>294573</v>
+        <v>139239</v>
       </c>
       <c r="J47" t="n">
-        <v>296078</v>
+        <v>148417</v>
       </c>
       <c r="K47" t="n">
-        <v>300917</v>
+        <v>150566</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Rīgā reģistrēto transportlīdzekļu skaits gada beigās. CSDD dati.</t>
+          <t>Pakalpojumu, rūpniecības un pārējo patērētāju (t. sk. lauksaimniecības) elektroenerģijas patēriņa CO2 emisijas. SEG aprēķinu tabula – dalījums patēriņa gala sektoros.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -2959,12 +2944,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Reģistrētie transportlīdzekļi ar elektromotoriem</t>
+          <t>Reģistrētie transportlīdzekļi, kopā</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2983,27 +2968,27 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1122</v>
+        <v>283627</v>
       </c>
       <c r="G48" t="n">
-        <v>1799</v>
+        <v>288527.8874</v>
       </c>
       <c r="H48" t="n">
-        <v>2721</v>
+        <v>290614.7807</v>
       </c>
       <c r="I48" t="n">
-        <v>3779</v>
+        <v>294573</v>
       </c>
       <c r="J48" t="n">
-        <v>5129</v>
+        <v>296078</v>
       </c>
       <c r="K48" t="n">
-        <v>7138</v>
+        <v>300917</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Rīgā reģistrēto transportlīdzekļu ar elektromotoriem skaits gada beigās. CSDD dati.</t>
+          <t>Rīgā reģistrēto transportlīdzekļu skaits gada beigās. CSDD dati.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3011,12 +2996,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Elektro uzlādes pieslēgvietu skaits Rīgā</t>
+          <t>Reģistrētie transportlīdzekļi ar elektromotoriem</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3034,13 +3019,28 @@
           <t>skaits</t>
         </is>
       </c>
+      <c r="F49" t="n">
+        <v>1122</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1799</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2721</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3779</v>
+      </c>
+      <c r="J49" t="n">
+        <v>5129</v>
+      </c>
       <c r="K49" t="n">
-        <v>537</v>
+        <v>7138</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Publiski pieejamo elektrotransporta uzlādes pieslēgvietu skaits Rīgā gada beigās.</t>
+          <t>Rīgā reģistrēto transportlīdzekļu ar elektromotoriem skaits gada beigās. CSDD dati.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3052,12 +3052,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Veloceļu garums</t>
+          <t>Elektro uzlādes pieslēgvietu skaits Rīgā</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3072,44 +3072,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>97.5633</v>
-      </c>
-      <c r="G50" t="n">
-        <v>125.3663</v>
-      </c>
-      <c r="H50" t="n">
-        <v>133.6304</v>
-      </c>
-      <c r="I50" t="n">
-        <v>150.5062</v>
-      </c>
-      <c r="J50" t="n">
-        <v>160.8782</v>
+          <t>skaits</t>
+        </is>
       </c>
       <c r="K50" t="n">
-        <v>165.0212</v>
+        <v>537</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Veloinfrastruktūras kopgarums Rīgā, kumulatīvi: 2020. g. garums + katru gadu izbūvētie posmi.</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>Publiski pieejamo elektrotransporta uzlādes pieslēgvietu skaits Rīgā gada beigās.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://www.transportdata.gov.lv/lv/card/978835ee-f55b-481c-9791-ba0395d3619a</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pārvadāto pasažieru skaits pa veidiem sabiedriskajā transportā</t>
+          <t>Veloceļu garums</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3119,36 +3108,36 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sabiedriskais</t>
+          <t>Transports, kopā</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>milj. pasažieru gadā</t>
+          <t>km</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>89.7</v>
+        <v>97.5633</v>
       </c>
       <c r="G51" t="n">
-        <v>74.3</v>
+        <v>125.3663</v>
       </c>
       <c r="H51" t="n">
-        <v>93.3</v>
+        <v>133.6304</v>
       </c>
       <c r="I51" t="n">
-        <v>114.7</v>
+        <v>150.5062</v>
       </c>
       <c r="J51" t="n">
-        <v>115.9701</v>
+        <v>160.8782</v>
       </c>
       <c r="K51" t="n">
-        <v>118.4919</v>
+        <v>165.0212</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Sabiedriskajā transportā pārvadāto pasažieru skaits gadā (autobuss, trolejbuss, tramvajs). Rīgas Satiksme dati.</t>
+          <t>Veloinfrastruktūras kopgarums Rīgā, kumulatīvi: 2020. g. garums + katru gadu izbūvētie posmi.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3156,12 +3145,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ikgadējais sabiedriskā transporta "Rīgas Satiksme" nobraukums maršrutu tīklā</t>
+          <t>Pārvadāto pasažieru skaits pa veidiem sabiedriskajā transportā</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3176,31 +3165,31 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>tūkst. km</t>
+          <t>milj. pasažieru gadā</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>37869.79</v>
+        <v>89.7</v>
       </c>
       <c r="G52" t="n">
-        <v>34486</v>
+        <v>74.3</v>
       </c>
       <c r="H52" t="n">
-        <v>33260</v>
+        <v>93.3</v>
       </c>
       <c r="I52" t="n">
-        <v>34682.333</v>
+        <v>114.7</v>
       </c>
       <c r="J52" t="n">
-        <v>35531.174</v>
+        <v>115.9701</v>
       </c>
       <c r="K52" t="n">
-        <v>35013.5329</v>
+        <v>118.4919</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Rīgas Satiksme transportlīdzekļu kopējais gada nobraukums maršrutu tīklā. Rīgas Satiksme dati.</t>
+          <t>Sabiedriskajā transportā pārvadāto pasažieru skaits gadā (autobuss, trolejbuss, tramvajs). Rīgas Satiksme dati.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3208,12 +3197,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AER īpatsvars sabiedriskā transporta sektorā</t>
+          <t>Ikgadējais sabiedriskā transporta "Rīgas Satiksme" nobraukums maršrutu tīklā</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3228,25 +3217,31 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>tūkst. km</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>16</v>
+        <v>37869.79</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34486</v>
+      </c>
+      <c r="H53" t="n">
+        <v>33260</v>
       </c>
       <c r="I53" t="n">
-        <v>32.8049</v>
+        <v>34682.333</v>
       </c>
       <c r="J53" t="n">
-        <v>34.286</v>
+        <v>35531.174</v>
       </c>
       <c r="K53" t="n">
-        <v>35.4465</v>
+        <v>35013.5329</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>AER īpatsvars Rīgas Satiksme sabiedriskā transporta enerģijas patēriņā. Rīgas Satiksme dati.</t>
+          <t>Rīgas Satiksme transportlīdzekļu kopējais gada nobraukums maršrutu tīklā. Rīgas Satiksme dati.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3254,12 +3249,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CO2 emisijas privātajā transportā</t>
+          <t>AER īpatsvars sabiedriskā transporta sektorā</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3269,36 +3264,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CO2 emisijas</t>
+          <t>Sabiedriskais</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>tCO2/gadā</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>674997</v>
-      </c>
-      <c r="G54" t="n">
-        <v>673869</v>
-      </c>
-      <c r="H54" t="n">
-        <v>675278</v>
+        <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>714604</v>
+        <v>32.8049</v>
       </c>
       <c r="J54" t="n">
-        <v>713848</v>
+        <v>34.286</v>
       </c>
       <c r="K54" t="n">
-        <v>720112.2285</v>
+        <v>35.4465</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Privātā autotransporta degvielas patēriņa CO2 emisijas. SEG inventarizācija.</t>
+          <t>AER īpatsvars Rīgas Satiksme sabiedriskā transporta enerģijas patēriņā. Rīgas Satiksme dati.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3306,12 +3295,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CO2 emisijas sabiedriskajā transportā (Rīgas Satiksme)</t>
+          <t>CO2 emisijas privātajā transportā</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3330,27 +3319,27 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>35364</v>
+        <v>674997</v>
       </c>
       <c r="G55" t="n">
-        <v>37156.3547</v>
+        <v>673869</v>
       </c>
       <c r="H55" t="n">
-        <v>36214.682</v>
+        <v>675278</v>
       </c>
       <c r="I55" t="n">
-        <v>37181.6078</v>
+        <v>714604</v>
       </c>
       <c r="J55" t="n">
-        <v>35952.2448</v>
+        <v>713848</v>
       </c>
       <c r="K55" t="n">
-        <v>34088.5997</v>
+        <v>720112.2285</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Rīgas Satiksme sabiedriskā transporta enerģijas (degvielas un elektroenerģijas) patēriņa CO2 emisijas. SEG inventarizācija.</t>
+          <t>Privātā autotransporta degvielas patēriņa CO2 emisijas. SEG inventarizācija.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -3358,12 +3347,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CO2 emisijas dzelzceļa transportā</t>
+          <t>CO2 emisijas sabiedriskajā transportā (Rīgas Satiksme)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3382,27 +3371,27 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3701</v>
+        <v>35364</v>
       </c>
       <c r="G56" t="n">
-        <v>4290</v>
+        <v>37156.3547</v>
       </c>
       <c r="H56" t="n">
-        <v>4397</v>
+        <v>36214.682</v>
       </c>
       <c r="I56" t="n">
-        <v>2285</v>
+        <v>37181.6078</v>
       </c>
       <c r="J56" t="n">
-        <v>2408</v>
+        <v>35952.2448</v>
       </c>
       <c r="K56" t="n">
-        <v>2347.5261</v>
+        <v>34088.5997</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Dzelzceļa transporta enerģijas patēriņa CO2 emisijas Rīgas teritorijā. SEG inventarizācija.</t>
+          <t>Rīgas Satiksme sabiedriskā transporta enerģijas (degvielas un elektroenerģijas) patēriņa CO2 emisijas. SEG inventarizācija.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -3410,12 +3399,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Transporta sektora CO2 emisijas, kopā</t>
+          <t>CO2 emisijas dzelzceļa transportā</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3434,27 +3423,27 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>717680</v>
+        <v>3701</v>
       </c>
       <c r="G57" t="n">
-        <v>719892</v>
+        <v>4290</v>
       </c>
       <c r="H57" t="n">
-        <v>719707</v>
+        <v>4397</v>
       </c>
       <c r="I57" t="n">
-        <v>755854</v>
+        <v>2285</v>
       </c>
       <c r="J57" t="n">
-        <v>753553</v>
+        <v>2408</v>
       </c>
       <c r="K57" t="n">
-        <v>757743</v>
+        <v>2347.5261</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kopā: 4008 + 4009 + 4010 + pašvaldības transports (rādītājs 1020).</t>
+          <t>Dzelzceļa transporta enerģijas patēriņa CO2 emisijas Rīgas teritorijā. SEG inventarizācija.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -3462,17 +3451,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pilsētas CO2 emisijas kopā</t>
+          <t>Transporta sektora CO2 emisijas, kopā</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kopā</t>
+          <t>Transports</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3486,27 +3475,27 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1628791</v>
+        <v>717680</v>
       </c>
       <c r="G58" t="n">
-        <v>1761653.543</v>
+        <v>719892</v>
       </c>
       <c r="H58" t="n">
-        <v>1615847.5284</v>
+        <v>719707</v>
       </c>
       <c r="I58" t="n">
-        <v>1604125.1273</v>
+        <v>755854</v>
       </c>
       <c r="J58" t="n">
-        <v>1606629.5896</v>
+        <v>753553</v>
       </c>
       <c r="K58" t="n">
-        <v>1573997.8421</v>
+        <v>757743</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>REA emisiju aprēķina tabula</t>
+          <t>Kopā: 4008 + 4009 + 4010 + pašvaldības transports (rādītājs 1020).</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -3514,12 +3503,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 1990. gadu, kopā</t>
+          <t>Pilsētas CO2 emisijas kopā</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3534,31 +3523,31 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>% pret bāzi</t>
+          <t>tCO2/gadā</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-62.0417</v>
+        <v>1628791</v>
       </c>
       <c r="G59" t="n">
-        <v>-58.9454</v>
+        <v>1761653.543</v>
       </c>
       <c r="H59" t="n">
-        <v>-62.3433</v>
+        <v>1615847.5284</v>
       </c>
       <c r="I59" t="n">
-        <v>-62.6165</v>
+        <v>1604125.1273</v>
       </c>
       <c r="J59" t="n">
-        <v>-62.5582</v>
+        <v>1606629.5896</v>
       </c>
       <c r="K59" t="n">
-        <v>-63.3186</v>
+        <v>1573997.8421</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Pilsētas kopējās CO2 emisijas (rādītājs 5001) pret 1990. g. bāzi 4291 kt: 5001 / bāze − 1.</t>
+          <t>REA emisiju aprēķina tabula</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -3566,12 +3555,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 2019. gadu, kopā</t>
+          <t>CO2 izmaiņas pret 1990. gadu, kopā</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3590,27 +3579,27 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-6.4988</v>
+        <v>-62.0417</v>
       </c>
       <c r="G60" t="n">
-        <v>1.1282</v>
+        <v>-58.9454</v>
       </c>
       <c r="H60" t="n">
-        <v>-7.2418</v>
+        <v>-62.3433</v>
       </c>
       <c r="I60" t="n">
-        <v>-7.9147</v>
+        <v>-62.6165</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.771</v>
+        <v>-62.5582</v>
       </c>
       <c r="K60" t="n">
-        <v>-9.6442</v>
+        <v>-63.3186</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Pilsētas kopējās CO2 emisijas (rādītājs 5001) pret 2019. g. bāzi 1742 kt: 5001 / bāze − 1.</t>
+          <t>Pilsētas kopējās CO2 emisijas (rādītājs 5001) pret 1990. g. bāzi 4291 kt: 5001 / bāze − 1.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3618,12 +3607,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 1990. gadu, enerģija</t>
+          <t>CO2 izmaiņas pret 2019. gadu, kopā</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3642,27 +3631,27 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-34.9206</v>
+        <v>-6.4988</v>
       </c>
       <c r="G61" t="n">
-        <v>-25.5885</v>
+        <v>1.1282</v>
       </c>
       <c r="H61" t="n">
-        <v>-35.99</v>
+        <v>-7.2418</v>
       </c>
       <c r="I61" t="n">
-        <v>-39.4092</v>
+        <v>-7.9147</v>
       </c>
       <c r="J61" t="n">
-        <v>-39.066</v>
+        <v>-7.771</v>
       </c>
       <c r="K61" t="n">
-        <v>-41.6961</v>
+        <v>-9.6442</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Enerģijas sektora CO2 emisijas (3012 + 3013 + 3014) pret 1990. g. bāzi 1400 kt: summa / bāze − 1.</t>
+          <t>Pilsētas kopējās CO2 emisijas (rādītājs 5001) pret 2019. g. bāzi 1742 kt: 5001 / bāze − 1.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -3670,12 +3659,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 2019. gadu, enerģija</t>
+          <t>CO2 izmaiņas pret 1990. gadu, enerģija</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3694,27 +3683,27 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-2.4506</v>
+        <v>-34.9206</v>
       </c>
       <c r="G62" t="n">
-        <v>11.5376</v>
+        <v>-25.5885</v>
       </c>
       <c r="H62" t="n">
-        <v>-4.0535</v>
+        <v>-35.99</v>
       </c>
       <c r="I62" t="n">
-        <v>-9.178699999999999</v>
+        <v>-39.4092</v>
       </c>
       <c r="J62" t="n">
-        <v>-8.664199999999999</v>
+        <v>-39.066</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.6065</v>
+        <v>-41.6961</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Enerģijas sektora CO2 emisijas (3012 + 3013 + 3014) pret 2019. g. bāzi 934 kt (SEG inventarizācija; SECAP 914 kt): summa / bāze − 1.</t>
+          <t>Enerģijas sektora CO2 emisijas (3012 + 3013 + 3014) pret 1990. g. bāzi 1400 kt: summa / bāze − 1.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -3722,12 +3711,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 1990. gadu, transports</t>
+          <t>CO2 izmaiņas pret 2019. gadu, enerģija</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3746,27 +3735,27 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>19.6133</v>
+        <v>-2.4506</v>
       </c>
       <c r="G63" t="n">
-        <v>19.982</v>
+        <v>11.5376</v>
       </c>
       <c r="H63" t="n">
-        <v>19.9512</v>
+        <v>-4.0535</v>
       </c>
       <c r="I63" t="n">
-        <v>25.9757</v>
+        <v>-9.178699999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>25.5922</v>
+        <v>-8.664199999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>26.2905</v>
+        <v>-12.6065</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Transporta sektora CO2 emisijas (rādītājs 4011) pret 1990. g. bāzi 600 kt: 4011 / bāze − 1.</t>
+          <t>Enerģijas sektora CO2 emisijas (3012 + 3013 + 3014) pret 2019. g. bāzi 934 kt (SEG inventarizācija; SECAP 914 kt): summa / bāze − 1.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -3774,12 +3763,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 2019. gadu, transports</t>
+          <t>CO2 izmaiņas pret 1990. gadu, transports</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3798,27 +3787,27 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>-11.1782</v>
+        <v>19.6133</v>
       </c>
       <c r="G64" t="n">
-        <v>-10.9045</v>
+        <v>19.982</v>
       </c>
       <c r="H64" t="n">
-        <v>-10.9274</v>
+        <v>19.9512</v>
       </c>
       <c r="I64" t="n">
-        <v>-6.4537</v>
+        <v>25.9757</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.7385</v>
+        <v>25.5922</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.2199</v>
+        <v>26.2905</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Transporta sektora CO2 emisijas (rādītājs 4011) pret 2019. g. bāzi 808 kt (SEG inventarizācija): 4011 / bāze − 1.</t>
+          <t>Transporta sektora CO2 emisijas (rādītājs 4011) pret 1990. g. bāzi 600 kt: 4011 / bāze − 1.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -3826,12 +3815,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CO2 izmaiņas pret 2019. gadu, pašvaldības sektors</t>
+          <t>CO2 izmaiņas pret 2019. gadu, transports</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3850,27 +3839,27 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>-0.1055</v>
+        <v>-11.1782</v>
       </c>
       <c r="G65" t="n">
-        <v>4.5725</v>
+        <v>-10.9045</v>
       </c>
       <c r="H65" t="n">
-        <v>-6.2388</v>
+        <v>-10.9274</v>
       </c>
       <c r="I65" t="n">
-        <v>-22.5343</v>
+        <v>-6.4537</v>
       </c>
       <c r="J65" t="n">
-        <v>-24.6993</v>
+        <v>-6.7385</v>
       </c>
       <c r="K65" t="n">
-        <v>-27.3105</v>
+        <v>-6.2199</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Pašvaldības sektora CO2 emisijas (1016–1020, t. sk. ūdensapgāde) pret 2019. g. bāzi 37,9 kt: summa / bāze − 1.</t>
+          <t>Transporta sektora CO2 emisijas (rādītājs 4011) pret 2019. g. bāzi 808 kt (SEG inventarizācija): 4011 / bāze − 1.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -3878,54 +3867,106 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>5008</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CO2 izmaiņas pret 2019. gadu, pašvaldības sektors</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kopā</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CO2 emisijas</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>% pret bāzi</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.1055</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.5725</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-6.2388</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-22.5343</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-24.6993</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-27.3105</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Pašvaldības sektora CO2 emisijas (1016–1020, t. sk. ūdensapgāde) pret 2019. g. bāzi 37,9 kt: summa / bāze − 1.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>LV-RESE</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>AER īpatsvars elektroenerģijā Latvijā (RES-E, Eurostat)</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Enerģija</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Elektroenerģija</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F67" t="n">
         <v>53.357</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G67" t="n">
         <v>51.399</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H67" t="n">
         <v>53.519</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I67" t="n">
         <v>54.317</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J67" t="n">
         <v>55.514</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K67" t="n">
         <v>57.6</v>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>2025: provizoriski</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4189,7 +4230,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46.85</v>
+        <v>45.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4197,7 +4238,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.2297</v>
+        <v>0.2101</v>
       </c>
       <c r="K4" t="n">
         <v>0.5455</v>
@@ -4278,7 +4319,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Netiešs: AER īpatsvars elektroenerģijā Latvijā (Eurostat RES-E; palīgdati 'Rādītāji - vērtības' rindā 78; 2025 – provizoriski). Pašvaldība izmanto tīkla elektroenerģiju; bāzes 54,36% atbilst valsts līmeņa rādītājam. Pašvaldības ēkās kopā uzstādīti 659,3 kWp saules paneļu (rādītājs 1010, kumulatīvi līdz 2025).</t>
+          <t>Netiešs: AER īpatsvars elektroenerģijā Latvijā (Eurostat RES-E; palīgdati 'Rādītāji - vērtības' rindā 79; 2025 – provizoriski). Pašvaldība izmanto tīkla elektroenerģiju; bāzes 54,36% atbilst valsts līmeņa rādītājam. Pašvaldības ēkās kopā uzstādīti 659,3 kWp saules paneļu (rādītājs 1010, kumulatīvi līdz 2025).</t>
         </is>
       </c>
     </row>
@@ -4386,13 +4427,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Nav datu</t>
+          <t>Sasniegts</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Nav datu par luksoforu patēriņu (mērķa gads 2024).</t>
+          <t>Veikta luksoforu diožu nomaiņa uz LED; dati par luksoforu vidējo elektroenerģijas patēriņu 2025. gadā nav pieejami (mērķa gads 2024).</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4497,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Netiešs: AER īpatsvars elektroenerģijā Latvijā (Eurostat RES-E; palīgdati 'Rādītāji - vērtības' rindā 78; 2025 – provizoriski). Nav datu par AER elektroenerģijas iepirkumu ielu apgaismojumam.</t>
+          <t>Netiešs: AER īpatsvars elektroenerģijā Latvijā (Eurostat RES-E; palīgdati 'Rādītāji - vērtības' rindā 79; 2025 – provizoriski). Nav atsevišķi datu par AER elektroenerģijas ielu apgaismojumam, vienots iepirkums.</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4728,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>46.85</v>
+        <v>45.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -4695,14 +4736,14 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.4529</v>
+        <v>0.4143</v>
       </c>
       <c r="K12" t="n">
         <v>0.5455</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Atbilst trajektorijai</t>
+          <t>Atpaliek no trajektorijas</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4727,12 +4768,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Samazināt relatīvos siltumenerģijas zudumus siltumtīklos</t>
+          <t>Samazināt relatīvos siltumenerģijas zudumus siltumtīklos aktīvajā apkures sezonā</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>&lt;10%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4742,7 +4783,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>– (gada zudumi 11,7%)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4751,25 +4792,32 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.49</v>
+        <v>9.77</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0.5455</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Netiek vērtēts</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>Sasniegts</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>AS "Rīgas siltums" Ilgtspējas pārskats: zudumi 12,49% – virs bāzes (11,7%) un mērķa (11,6%). Relatīvie zudumi katru gadu ir atkarīgi no klimatiskajiem apstākļiem (āra temperatūra, apkures sezonas ilgums), tāpēc gadu vērtības nav tieši salīdzināmas. Jāpārskata mērķis.</t>
+          <t>Rādītājs 3003. Mērķis vidusposmā mainīts atbilstoši NEKP2030 pasākuma 3.1.3.11 rezultatīvajam rādītājam (siltuma zudumu īpatsvars apkures sezonā &lt; 10 % līdz 2030. gadam); tāda pati norma iekļauta CSS attīstības stratēģijas 2026.–2040. gadam konceptuālajā ziņojumā. SECAP2030 sākotnējais mērķis – relatīvie gada zudumi 11,6 % (bāze 11,7 %, 2019). Zudumus būtiski ietekmē laikapstākļi: 2024./2025. finanšu gadā 12,49 % gadā un 9,77 % apkures sezonā; 2025./2026. finanšu gadā 11,8 % un 9,30 % (AS “Rīgas siltums” dati).</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4876,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Rādītājs 3006 (decentralizētā kurināmā patēriņš / kopējais siltumenerģijas galapatēriņš; SEG inventarizācija, Kopā_2025 rinda 67 / rinda 24). 2025. g. – 42,7%. Bāze atšķiras no SECAP: SECAP bāzi 44% (2019) nevar atkārtot ar inventarizācijas datiem, tāpēc progress mērīts pret 2020. g. vērtību, kas aprēķināta pēc tās pašas metodes (49,9%). Mērķis 40% nav mainīts.</t>
+          <t>Rādītājs 3007 (decentralizētā kurināmā patēriņš / kopējais siltumenerģijas galapatēriņš; SEG inventarizācija, Kopā_2025 rinda 67 / rinda 24). 2025. g. – 42,7%. Bāze atšķiras no SECAP: SECAP bāzi 44% (2019) nevar atkārtot ar inventarizācijas datiem, tāpēc progress mērīts pret 2020. g. vērtību, kas aprēķināta pēc tās pašas metodes (49,9%). Mērķis 40% nav mainīts.</t>
         </is>
       </c>
     </row>
@@ -4887,17 +4935,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Nav progresa</t>
+          <t>Atpaliek no trajektorijas</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Rādītājs 3007 (AER – biomasa ārpus CSS un mājsaimniecību AER – īpatsvars decentralizētā kurināmā patēriņā; SEG inventarizācija). 2025. g. – 34,2%. Bāze atšķiras no SECAP: progress mērīts pret 2020. g. vērtību pēc inventarizācijas (41,8%; SECAP 42%, 2019). Gada vērtības svārstās (34–43%), jo mainās biomasas sadalījums starp CSS un decentralizēto apgādi.</t>
+          <t>Rādītājs 3008 (AER – biomasa ārpus CSS un mājsaimniecību AER – īpatsvars decentralizētā kurināmā patēriņā; SEG inventarizācija). 2025. g. – 34,2%. Bāze atšķiras no SECAP: progress mērīts pret 2020. g. vērtību pēc inventarizācijas (41,8%; SECAP 42%, 2019). Gada vērtības svārstās (34–43%), jo mainās biomasas sadalījums starp CSS un decentralizēto apgādi.</t>
         </is>
       </c>
     </row>
@@ -4956,12 +5004,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Rādītājs 3005, GWh. SECAP bāzes vērtība 362 429 tūkst. m3 atbilst GASO 2020. gada datiem (30 856 + 331 573), tāpēc salīdzināts ar 2020. gadu.</t>
+          <t>Rādītājs 3006, GWh. SECAP bāzes vērtība 362 429 tūkst. m3 atbilst GASO 2020. gada datiem (30 856 + 331 573), tāpēc salīdzināts ar 2020. gadu.</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5068,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Rādītājs 3009.</t>
+          <t>Rādītājs 3010.</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5187,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Nav rādītāja (nepieciešams mobilitātes pētījums).</t>
+          <t>Nav salīdzināmu datu: SECAP bāze 42,4% ir braucienu īpatsvars (SUMBA mājsaimniecību aptauja, 2019). Indikatīvi – PAD sabiedriskā transporta maršrutu tīkla reformas pētījuma aptaujā (Kantar, 2025. g. sept., n=2500) 48% Rīgas iedzīvotāju regulāri (2–3 reizes nedēļā vai biežāk) brauc ar privāto auto, 51% regulāri izmanto sabiedrisko transportu; aptauja mēra izmantošanas biežumu, nevis braucienu sadalījumu. Nepieciešama braucienos balstīta mobilitātes aptauja.</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5494,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>statuss (darba versija)</t>
+          <t>statuss</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -5704,7 +5752,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pārskatā: “Plāna izstrāde vēl nav uzsākta.” (Pašvaldības ēku atjaunošanas plāns; daudzdzīvokļu ēku plāns – sk. Dz2.)</t>
+          <t>Plāna izstrāde vēl nav uzsākta (pašvaldības ēku atjaunošanas plāns; daudzdzīvokļu ēku plāns – sk. Dz2).</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -6027,7 +6075,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Izvērtēti scenāriji, gatavots ESKO iepirkums; par citām darbībām nepieciešama informācija.</t>
+          <t>Izvērtēti scenāriji, gatavots ESKO iepirkums, luksoforu diodes nomainītas uz LED; par pārējām darbībām informācija tiks papildināta.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -6047,7 +6095,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Plānā paredzēts 2022.–2023. gadā sagatavot investīciju plānu ielu apgaismojuma, elektrotīklu un balstu nomaiņai, izvērtējot arī iespēju slēgt ilgtermiņa energoefektivitātes pakalpojuma līgumu, jo 89 % ielu apgaismojuma veido nātrija spuldzes, kuru nomaiņa esošajā tempā aizņemtu vairākus gadus. Ielu apgaismojuma sadaļā plāns min arī vairākas papildu darbības – 45 dzīvsudraba gaismekļu nomaiņu, atlikušo luksoforu kvēlspuldžu nomaiņu uz LED, citu institūciju apsaimniekošanā esošo gaismekļu pārņemšanu un attālinātas viedās vadības sistēmas ieviešanu; informācija par to izpildi tiks papildināta.</t>
+          <t>Plānā paredzēts 2022.–2023. gadā sagatavot investīciju plānu ielu apgaismojuma, elektrotīklu un balstu nomaiņai, izvērtējot arī iespēju slēgt ilgtermiņa energoefektivitātes pakalpojuma līgumu, jo 89 % ielu apgaismojuma veido nātrija spuldzes, kuru nomaiņa esošajā tempā aizņemtu vairākus gadus. Ielu apgaismojuma sadaļā plāns min arī vairākas papildu darbības – 45 dzīvsudraba gaismekļu nomaiņu, atlikušo luksoforu kvēlspuldžu nomaiņu uz LED, citu institūciju apsaimniekošanā esošo gaismekļu pārņemšanu un attālinātas viedās vadības sistēmas ieviešanu. Luksoforu diožu nomaiņa uz LED ir veikta, bet informācija par pārējo darbību izpildi tiks papildināta.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -6143,7 +6191,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Modernizācijas projekti saskaņā ar Investīciju plānu (skaits jāpapildina).</t>
+          <t>Investīciju plānā 2026.–2027. gadam – 29 apgaismojuma projekti, t. sk. 10 apgaismojuma izbūves projekti neapgaismotās vietās.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -6168,7 +6216,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Saskaņā ar Investīciju plānā sniegto informāciju Rīgā tiek īstenoti … apgaismojuma modernizācijas projekti.</t>
+          <t>Saskaņā ar Investīciju plānā 2026.–2027. gadam sniegto informāciju Rīgā tiek īstenoti vai plānoti 29 ielu un pilsētvides apgaismojuma projekti (indikatīvi 75 milj. EUR): 10 apgaismojuma izbūves projekti līdz šim neapgaismotās vietās (4,2 milj. EUR) un 19 esošā apgaismojuma modernizācijas un atjaunošanas projekti (70,8 milj. EUR), t. sk. ielu apgaismes modernizācija un energoefektivitātes paaugstināšana visā pilsētā (60 milj. EUR). Četri projekti jau tiek īstenoti, pārējie ir apstiprināti plānā.</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6417,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pārskatā: “Pasākums netiek īstenots.”</t>
+          <t>Pasākums netiek īstenots.</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -6545,7 +6593,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pārskatā: “Pasākums daļēji īstenots.”</t>
+          <t>Pasākums daļēji īstenots.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -6934,14 +6982,10 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3001, 3012</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+          <t>3001, 3013</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Plānā paredzēts turpināt efektivitātes uzlabojumus AS “Rīgas siltums” 44 energoavotos un izvērtēt stingrākas efektivitātes prasības citiem operatoriem, no kuriem tiek iepirkta siltumenerģija. Pasākumam būtu jānodrošina 101 MWh ietaupījums un 15 tCO₂ samazinājums gadā.</t>
@@ -6950,7 +6994,8 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>2025. gada beigās Rīgas CSS bija uzstādīti 2,6 GW siltumražošanas jaudas, no kurām lielāko daļu veido dabasgāzes ūdenssildāmie katli (1 564 MW) un koģenerācijas stacijas (212 MW), vienlaikus 45 % saražotās siltumenerģijas bija atjaunīgas izcelsmes. CSS attīstības stratēģijā ieteikts veikt padziļinātu esošo siltumavotu izvērtējumu un uzturēt pastāvīgu to efektivitātes rādītāju monitoringu (rīcībpolitika 02-2).
-AS “Rīgas siltums” SC “Imanta” nomainīts absorbcijas siltumsūknis dūmgāzu siltuma atgūšanai (aplēstais ietaupījums ~5 000 MWh dabasgāzes un ~1 000 tCO₂ gadā), un līdz 2027. gadam plānota biokurināmā katlumājas modernizācija ar absorbcijas siltumsūkņiem (~5 milj. EUR). Uzņēmuma energopārvaldības sistēma sertificēta atbilstoši ISO 50001 (2021, resertifikācija 2024).</t>
+AS “Rīgas siltums” SC “Imanta” nomainīts absorbcijas siltumsūknis dūmgāzu siltuma atgūšanai (aplēstais ietaupījums ~5 000 MWh dabasgāzes un ~1 000 tCO₂ gadā), un līdz 2027. gadam plānota biokurināmā katlumājas modernizācija ar absorbcijas siltumsūkņiem (~5 milj. EUR). Uzņēmuma energopārvaldības sistēma sertificēta atbilstoši ISO 50001 (2021, resertifikācija 2024).
+AS “Rīgas siltums” SC “Imanta” uzstādīts un ekspluatācijā nodots 49 MW elektrodu katls, kas ļauj efektīvāk izmantot elektroenerģiju periodos, kad tās cena ir zema, īpaši kombinācijā ar plānoto siltumenerģijas akumulācijas tvertni (sk. E5). Lai energoavotu efektivitāte turpinātu pieaugt, REA jāturpina sadarbība ar siltumenerģijas ražotājiem un jāpalielina izpētes un pilotprojektu skaits.</t>
         </is>
       </c>
     </row>
@@ -6997,7 +7042,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3002, 3003</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -7013,7 +7058,7 @@
       <c r="O27" t="inlineStr">
         <is>
           <t>2025. gadā CSS turpgaitas temperatūra vidēji bija 69,5 °C, atgaitas – 43,4 °C. CSS attīstības stratēģijā ieteikts izpētīt teritorijas, kurās iespējams ieviest zemas temperatūras režīmu, un īstenot zemas temperatūras pilotprojektus (rīcībpolitika 03-1).
-AS “Rīgas siltums” turpina 4. paaudzes CSS projektus: zemas temperatūras grafiks ieviests, piem., A. Čaka ielā 123 un K. Barona ielā 112, uzsākts pieslēgums apbūves projektam Mežaparkā un Čiekurkalnā, un nākamajā periodā plānots pieslēgt RTU. 2024./2025. finanšu gadā izbūvēti, pārbūvēti vai atjaunoti 11,05 km siltumtīklu (aplēstais zudumu samazinājums 10 373 MWh un 1 224 tCO₂ gadā); 66 % uzņēmuma 768 km siltumtīklu ir pārbūvēti vai jaunizbūvēti. Zudumi apkures sezonā bija 9,7 %, gadā – 12,49 %. Tīklu modernizācijai noslēgts līgums ar Eiropas Padomes Attīstības banku par 40 milj. EUR investīciju portfeli.</t>
+AS “Rīgas siltums” turpina 4. paaudzes CSS projektus: zemas temperatūras grafiks ieviests, piem., A. Čaka ielā 123 un K. Barona ielā 112, uzsākts pieslēgums apbūves projektam Mežaparkā un Čiekurkalnā, un nākamajā periodā plānots pieslēgt RTU. 2024./2025. finanšu gadā izbūvēti, pārbūvēti vai atjaunoti 11,05 km siltumtīklu (aplēstais zudumu samazinājums 10 373 MWh un 1 224 tCO₂ gadā); 66 % uzņēmuma 768 km siltumtīklu ir pārbūvēti vai jaunizbūvēti. Zudumi aktīvajā apkures sezonā bija 9,77 %, gadā – 12,49 %. Tīklu modernizācijai noslēgts līgums ar Eiropas Padomes Attīstības banku par 40 milj. EUR investīciju portfeli.</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7103,11 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>ENABLE DHC (https://rea.riga.lv/projekti/enable-dhc/)</t>
@@ -7099,7 +7148,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elektrodu katls SC “Imanta”, plānotas jaunas AER jaudas.</t>
+          <t>Elektrodu katls SC “Imanta”, biokurināmā katlu māja Rencēnu ielā, plānotas jaunas AER jaudas.</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -7119,14 +7168,10 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3002, 3012</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+          <t>3002, 3013</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Plānā paredzēts izvērtēt saules sistēmu un siltumsūkņu izmantošanu AS “Rīgas siltums” 36 mazas jaudas dabasgāzes katlu mājās (kopā 29,5 MW) un siltuma pārpalikuma izmantošanu no deviņiem identificētajiem avotiem. Pasākumiem būtu jānodrošina AER pieaugums par 401 883 MWh/gadā un 81 180 tCO₂ samazinājums.</t>
@@ -7135,8 +7180,10 @@
       <c r="O29" t="inlineStr">
         <is>
           <t>Labā krasta apvienotajā zonā līdz 2028. gadam plānots ieviest 50 MW biomasas ūdenssildāmo katlu, 10 MW elektrodu katlu un 10 MW siltumsūkni, kas pēc stratēģijas aplēsēm samazinās CSS ražošanas emisijas no aptuveni 369 līdz 242 ktCO₂. Ambiciozais scenārijs līdz 2040. gadam paredz 396 MW jaunu AER jaudu, t. sk. 211 MW siltumsūkņu un elektrodu katlu.
+Lai veicinātu energoefektivitāti un vietējo AER izmantošanu centralizētajā siltumapgādē, 2023. gada nogalē tika īstenots projekts “Biokurināmā katlu mājas ar jaudu 48 MW izbūve Rencēnu ielā 30, Rīgā” ar 4 000 000 EUR Eiropas Kohēzijas fonda līdzfinansējumu.
 AS “Rīgas siltums” koncerns 2024./2025. finanšu gadā saražoja 48 % no Rīgas CSS nodotās siltumenerģijas – 70 % ar šķeldu (1 022 GWh), 30 % ar dabasgāzi; pārējo siltumenerģiju iepērk no neatkarīgajiem ražotājiem. SC “Imanta” 2025. gadā nodots ekspluatācijā 49 MW elektrodu katls (~20 GWh siltumenerģijas un ~4 000 tCO₂ ietaupījums gadā), un līdz 2028. gadam plānota 8 000 m³ (420 MWh) siltumakumulācijas tvertne. Uzņēmuma mērķis ir līdz 2030. gadam samazināt neto emisijas par 60 % pret 2019. gadu un sasniegt 70–80 % klimatneitrālas enerģijas īpatsvaru.
-AS “Rīgas siltums” uzstādījis trīs saules enerģijas stacijas ar kopējo jaudu 463,74 kW. AER risinājumus – saules paneļus un kolektorus – plānots ieviest mazas jaudas katlu mājās, kur tas ir tehniski un ekonomiski pamatoti.</t>
+AS “Rīgas siltums” uzstādījis trīs saules enerģijas stacijas ar kopējo jaudu 463,74 kW. AER risinājumus – saules paneļus un kolektorus – plānots ieviest mazas jaudas katlu mājās, kur tas ir tehniski un ekonomiski pamatoti.
+ES fondu projekts 4.3.1.0/22/A/001 “Biokurināmā katlu mājas ar jaudu 48 MW izbūve Rencēnu ielā 30, Rīgā”</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7237,7 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>Kā inovatīvi projekti izceļami AS “Rīgas siltums” SC “Imanta” uzstādītais 49 MW elektrodu katls, kā arī atlikumsiltuma izmantošanas izpēte un pilotēšana sadarbībā ar REA.
-Atlikumsiltums Rīgas CSS pagaidām praktiski netiek izmantots. Ambiciozajā scenārijā tā īpatsvars 2035. gadā sasniegtu 5,5 %, tuvojoties ES Elektrifikācijas rīcības plāna orientējošajam līmenim, ja attīstās datu centri un citi atlikumsiltuma avoti un tiek izveidots ekonomiski dzīvotspējīgs sadarbības modelis ar CSS. Izaugsmes un Ambiciozajā scenārijā paredzēta arī Daugavgrīvas notekūdeņu attīrīšanas iekārtu atlikumsiltuma (6 MW) integrācija.
+Atlikumsiltums no datu centriem un citiem ārējiem avotiem Rīgas CSS pagaidām praktiski netiek izmantots. Ambiciozajā scenārijā tā īpatsvars 2035. gadā sasniegtu 5,5 %, tuvojoties ES Elektrifikācijas rīcības plāna orientējošajam līmenim, ja attīstās datu centri un citi atlikumsiltuma avoti un tiek izveidots ekonomiski dzīvotspējīgs sadarbības modelis ar CSS. Izaugsmes un Ambiciozajā scenārijā paredzēta arī Daugavgrīvas notekūdeņu attīrīšanas iekārtu atlikumsiltuma (6 MW) integrācija.
 Projektā ENABLE DHC sadarbībā ar REA un SIA “Rīgas ūdens” veikta tehniski ekonomiskā izpēte siltuma atgūšanai no BAS “Daugavgrīva” un tā integrācijai Daugavgrīvas un Bolderājas CSS zonās; notiek scenāriju modelēšana. Kopā ar SIA “Tet” izvērtēti atlikumsiltuma un dzesēšanas risinājumi, un identificēts maza mēroga pilotprojekts.</t>
         </is>
       </c>
@@ -7235,11 +7282,7 @@
           <t>3001</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Plānā paredzēts paaugstināt CSS īpatsvaru kopējā siltumenerģijas pieprasījumā no 56 % (2020) līdz 60 %, izstrādājot standarta risinājumus un atbalsta mehānismus pieslēgumiem, grozot RD saistošos noteikumus Nr. 97 par sadedzināšanas iekārtu izvēli, īstenojot informatīvus pasākumus un atbalsta programmu iedzīvotājiem. Pasākumam nav paredzēts tiešs enerģijas ietaupījums un CO₂ emisiju samazinājums.</t>
@@ -7247,10 +7290,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026. gada aprīlī CSS bija 8431 pieslēgums, un siltumtīklu kopgarums bija aptuveni 948 km. Jaunu tīklu izbūves temps pieaug – no 2,8 km 2022. gadā līdz 5,3 km 2025. gadā –, tomēr tīklu paplašināšanās (0,6 % gadā) ir krietni lēnāka par ES Elektrifikācijas rīcības plānā paredzēto (6–7 % gadā). CSS pieslēgti 58 % apsildāmās ēku platības, bet pēc stratēģijas aplēsēm CSS nodrošina ap 53 % no kopējā siltumenerģijas pieprasījuma (SECAP2030: 56 % 2020. gadā, mērķis – 60 %); atšķirība daļēji skaidrojama ar atšķirīgu aprēķina metodi. Kā perspektīvākās CSS attīstības teritorijas stratēģijā izceltas VEF, Skanste, Pārdaugava, Ķengarags un Bieriņi.
+          <t>Lai veicinātu jaunu klientu pieslēgšanu Rīgas pilsētas CSS ar mērķi uzlabot dabas aizsardzību un bioloģisko daudzveidību, “zaļo” infrastruktūru, it īpaši pilsētvidē, un samazināt piesārņojumu, AS “Rīgas siltums” iesaistījās projektā “Gaisa piesārņojuma samazināšanas pasākumi Rīgas valstspilsētas pašvaldībā”. Tas ļāva piesaistīt 2 535 430 EUR ERAF finansējuma siltumtīklu izbūvei, lai pieslēgtu objektus CSS.
+2026. gada aprīlī CSS bija 8431 pieslēgums, un siltumtīklu kopgarums bija aptuveni 948 km. Jaunu tīklu izbūves temps pieaug – no 2,8 km 2022. gadā līdz 5,3 km 2025. gadā –, tomēr tīklu paplašināšanās (0,6 % gadā) ir krietni lēnāka par ES Elektrifikācijas rīcības plānā paredzēto (6–7 % gadā). CSS pieslēgti 58 % apsildāmās ēku platības, bet pēc stratēģijas aplēsēm CSS nodrošina ap 53 % no kopējā siltumenerģijas pieprasījuma (SECAP2030: 56 % 2020. gadā, mērķis – 60 %); atšķirība daļēji skaidrojama ar atšķirīgu aprēķina metodi. Kā perspektīvākās CSS attīstības teritorijas stratēģijā izceltas VEF, Skanste, Pārdaugava, Ķengarags un Bieriņi.
 2024./2025. finanšu gadā CSS pieslēgtas 56 jaunas ēkas ar kopējo siltumslodzi 22,5 MW (44 labajā krastā, 12 kreisajā), un jaunu klientu pieslēgšanai izbūvēti 2,67 km siltumtīklu.
 Pieejams līdzfinansējums, tiek veikts komunikācijas darbs.
-Tiek uzturēts apkures katlu reģistrs.</t>
+Tiek uzturēts apkures katlu reģistrs.
+ES fondu projekts 2.2.3.5/1/24/I/002 “Gaisa piesārņojuma samazināšanas pasākumi Rīgas valstspilsētas pašvaldībā”</t>
         </is>
       </c>
     </row>
@@ -7297,14 +7342,10 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3003, 3014, 3006, 3007</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
+          <t>3004, 3015, 3007, 3008</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Plānā paredzēts pakāpeniski, ne vēlāk kā līdz 2025. gadam, pārtraukt atļauju izsniegšanu fosilā kurināmā iekārtām ar jaudu līdz 0,2 MW, lielākām iekārtām noteikt prioritāro secību (pieslēgums CSS, AER tehnoloģijas, no 2030. gada dabasgāze tikai ar oglekļa uztveršanu) un izvērtēt principa “piesārņotājs maksā” piemērošanu. Pasākumam būtu jānodrošina AER pieaugums par 166 486 MWh/gadā un 46 199 tCO₂ samazinājums 2030. gadā.</t>
@@ -7359,7 +7400,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3009, 3010, 3011, 1010</t>
+          <t>3010, 3011, 3012, 1010</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -7498,11 +7539,7 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Plānā paredzēts izpētīt pašvaldības darbinieku mobilitātes paradumus, nodrošināt koplietošanas darba telpas pašvaldības ēkās un attālinātā darba vietas mikrorajonos un Pierīgā, kā arī turpināt attīstīt e-pakalpojumu portālu eriga.lv. Pasākumiem T1 un T2 kopā būtu jānodrošina 185 000 MWh enerģijas ietaupījums un 45 300 tCO₂ samazinājums gadā (plānā norādīts kopējs rādītājs, sk. T1).</t>
@@ -7623,11 +7660,7 @@
           <t>4005, 4006</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Plānā paredzēta sabiedriskā transporta pieejamības un kvalitātes uzlabošana (Rīgas un Pierīgas sistēmu integrācija, stāvparki, vienotā biļete, sabiedriskā transporta joslas), ritošā sastāva modernizācija, dzelzceļa izmantošanas veicināšana un maršrutu tīkla optimizācija. Sabiedriskā transporta īpatsvara pieaugumam līdz 20 % no pasažierkilometriem būtu jānodrošina 185 700 MWh enerģijas ietaupījums un 49 600 tCO₂ samazinājums gadā.</t>
@@ -7636,6 +7669,8 @@
       <c r="O37" t="inlineStr">
         <is>
           <t>2025. gadā “Rīgas satiksme” pārvadāja 118,5 milj. pasažieru (2023. gadā – 114,74 milj., 2024. gadā – 115,97 milj.). Pakalpojums tiek nodrošināts 79 tramvaju, trolejbusu un autobusu maršrutos ar kopējo maršrutu tīkla garumu 1 166,3 km; izpildīti 99,68 % reisu, un vidējais braukšanas ātrums pieaudzis līdz 20,03 km/h (2024. gadā – 19,53 km/h). Ar pakalpojuma pieejamību apmierināti 82 %, ar kvalitāti – 77 % klientu. 2025. gadā veiktas izmaiņas maršrutu tīklā, izveidoti jauni tramvaju savienojumi, un izmēģinājuma pievedošie maršruti pieņemti kā pastāvīgi. Nakts sabiedriskā transporta pilotprojektā pārvadāti 11 422 pasažieri. Metropoles mobilitātes integrācijai ieviesta Rīgas vienotā biļete ar “Pasažieru vilcienu” un noslēgts trīspusējs līgums starp Rīgas valstspilsētu, “Rīgas satiksmi” un Ropažu novadu – pirmais starppašvaldību sabiedriskā transporta līdzfinansēšanas modelis Latvijā. 2026. gada 1. jūnijā atklāts 7. tramvaja līnijas pagarinājums (2,2 km) līdz mobilitātes punktam “Ķengarags”, ko apkalpo 7. un 14. tramvajs, 15. trolejbuss un 49. autobuss. 2026. gadā plānots uzsākt priekšizpētes tramvaja līniju būvniecībai Skanstes un Ziepniekkalna apkaimēs.
+PAD maršrutu tīkla reformas pētījumā secināts, ka sistēmai ir plašs pārklājums (90 % iedzīvotāju dzīvo 400 m attālumā no pieturas) un augsta precizitāte (94 % reisu kavējas ne vairāk kā 5 minūtes), taču maršrutu tīkls nav būtiski pārskatīts vairāk nekā 30 gadus un ir izteikti orientēts uz centru: radiālie maršruti veido 58 % tīkla, vairāk nekā 55 % maršrutu maksimuma stundās kursē ar 20 minūšu vai lielāku intervālu, un darba braucienos starp apkaimēm ārpus centra sabiedriskā transporta īpatsvars bieži ir zem 10 %. Prioritātes pasākumu (sabiedriskā transporta joslas, prioritāte luksoforos) ir salīdzinoši maz. Pētījumā ieteikts veidot skaidrāku, hierarhisku tīklu ar spēcīgiem maģistrālajiem koridoriem, vienlaikus uzlabojot starpapkaimju savienojumus, un pilotēt ekspresreisus (piem., Brīvības ielas koridorā), jaunus starpapkaimju maršrutus un pieturu optimizāciju.
+Aptaujā 68 % iedzīvotāju pozitīvi vērtē sabiedriskā transporta atbilstību savām vajadzībām; svarīgākās ir precizitāte un regularitāte, un 58 % pasažieru piekristu braucieniem ar pārsēšanos, ja transports kursētu biežāk. Vienlaikus 6 % plāno sabiedrisko transportu izmantot biežāk, bet 13 % – retāk vai to pārtraukt, galvenokārt, lai vairāk brauktu ar automašīnu.
 Atveseļošanas fonda transporta zaļināšanas reformā plānotā metrobusa līnija Dzelzavas ielā 2024. gadā netika īstenota, un tās finansējums novirzīts Rail Baltica projektam.</t>
         </is>
       </c>
@@ -7703,7 +7738,8 @@
       <c r="O38" t="inlineStr">
         <is>
           <t>Zemo emisiju zonas projekta (PAD pārziņā) tālāka virzība kopš 2026. gada pavasara ir apturēta. Zona bija viena no REA vadītā NetZeroCities pilotprojekta SEED galvenajām tēmām – sadarbībā ar partneriem īstenoti gaisa kvalitātes mērījumi, iesaistot skolēnus, un mobilitātes paradumi apspriesti fokusgrupās un aptaujās; rezultāti noderēja arī zonas projekta vadītājiem. Jāņem vērā, ka zemo emisiju zonas primārais mērķis ir gaisa kvalitātes uzlabošana, un tai nav viennozīmīgi lielākā ietekme uz pilsētas SEG emisijām.
-2026. gada augustā rosināts izveidot Rīgas autonovietņu un mobilitātes attīstības komisiju, kuras pirmais uzdevums būtu stāvparku plānošana pie pilsētas robežas un lielākajiem transporta mezgliem. Tiek apspriestas arī izmaiņas stāvvietu regulējumā, t. sk. elektroauto bezmaksas stāvēšanas priekšrocību pakāpeniska ierobežošana no 2027. gada.</t>
+2026. gada augustā rosināts izveidot Rīgas autonovietņu un mobilitātes attīstības komisiju, kuras pirmais uzdevums būtu stāvparku plānošana pie pilsētas robežas un lielākajiem transporta mezgliem. Tiek apspriestas arī izmaiņas stāvvietu regulējumā, t. sk. elektroauto bezmaksas stāvēšanas priekšrocību pakāpeniska ierobežošana no 2027. gada.
+Maršrutu tīkla reformas pētījumā secināts, ka piekļuve centram ar automašīnu joprojām ir ērta – stāvvietu piedāvājums ir plašs, maksa tiek uztverta kā zema, un Rīgā nav izveidota stāvparku (P&amp;R) sistēma. Biežākais iemesls sabiedriskā transporta izmantošanai aptaujā (46 %) ir tas, ka nav jāmeklē un jāapmaksā stāvvieta. Līdz 2030. gadam ieteikts pilotēt stāvparkus pie galvenajiem iebraukšanas ceļiem ar biežu sabiedrisko transportu (piem., Juglā), pakāpeniski samazināt stāvvietu skaitu un pārskatīt cenas centrā, kā arī jaunās attīstības teritorijās ar labu sabiedriskā transporta pieejamību noteikt zemākus maksimālos stāvvietu normatīvus.</t>
         </is>
       </c>
     </row>
@@ -7757,11 +7793,7 @@
           <t>4001, 4008</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Plānā paredzēta mobilitātes punktu attīstība, atbalsts koplietošanas transportlīdzekļu uzņēmumiem un koncepta “mobilitāte kā pakalpojums” attīstība Rīgā. Pasākumiem T5 un T6 kopā būtu jānodrošina 131 500 MWh enerģijas ietaupījums un 32 440 tCO₂ samazinājums gadā (plānā norādīts kopējs rādītājs, sk. T5).</t>
@@ -7769,7 +7801,8 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Rīgā izveidots 15 mobilitātes punktu tīkls pie dzelzceļa stacijām un pieturām (ES kohēzijas politikas 2021–2027 pasākums 2.3.1.2 “Multimodāls sabiedriskā transporta tīkls”). 2026. gada septembrī Rīgas dome atbalstīja vēl desmit mobilitātes punktu izveidi līdz 2029. gada beigām (līdz 26,6 milj. EUR, t. sk. 15 milj. EUR ERAF), tostarp pie Centrālās stacijas un Starptautiskās autoostas. https://www.riga.lv/lv/mobilitates-punktu-buvnieciba</t>
+          <t>Rīgā izveidots 15 mobilitātes punktu tīkls pie dzelzceļa stacijām un pieturām (ES kohēzijas politikas 2021–2027 pasākums 2.3.1.2 “Multimodāls sabiedriskā transporta tīkls”). 2026. gada septembrī Rīgas dome atbalstīja vēl desmit mobilitātes punktu izveidi līdz 2029. gada beigām (līdz 26,6 milj. EUR, t. sk. 15 milj. EUR ERAF), tostarp pie Centrālās stacijas un Starptautiskās autoostas. https://www.riga.lv/lv/mobilitates-punktu-buvnieciba
+Maršrutu tīkla reformas pētījuma dati liecina, ka koplietošanas mobilitāte pašlaik konsekventi nedarbojas kā pirmā/pēdējā kilometra risinājums sabiedriskajam transportam: koplietošanas automašīnas bieži aizstāj braucienus uz teritorijām ārpus sabiedriskā transporta pārklājuma, bet mikromobilitātes braucieni koncentrējas centrā. Pētījumā ieteikts pilnveidot mobilitātes punktus un savienojumus ar dzelzceļu – aptaujā biežāku sabiedriskā transporta lietošanu plāno tieši vilciena un mikromobilitātes lietotāji.</t>
         </is>
       </c>
     </row>
@@ -7822,11 +7855,7 @@
           <t>4002, 4003</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Plānā paredzēts saglabāt esošās priekšrocības ETL (bezmaksas stāvvietas, sabiedriskā transporta joslas), attīstīt uzlādes infrastruktūru pie pašvaldības iestādēm, publiskās vietās un pie daudzdzīvokļu ēkām, sniegt atbalstu ETL iegādei un izpētīt alternatīvo degvielu potenciālu. ETL īpatsvara pieaugumam līdz 5 % autoparka būtu jānodrošina 74 000 MWh enerģijas ietaupījums, 14 200 MWh AER un 22 080 tCO₂ samazinājums gadā.</t>
@@ -7879,11 +7908,7 @@
           <t>1014, 1015</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Plānā paredzēts izvērtēt pašvaldības funkcijas nodrošinošo transportlīdzekļu (piem., atkritumu apsaimniekošanas transporta) pakāpenisku pāreju uz tīrām tehnoloģijām un iespējamo pašvaldības atbalstu. Pasākumam nav paredzēts tiešs enerģijas ietaupījums un CO₂ emisiju samazinājums.</t>
@@ -7996,11 +8021,7 @@
           <t>4007, 4009</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Plānā paredzēta bezizmešu autobusu un zemās grīdas tramvaju iegāde un elektroautobusu uzlādes infrastruktūras izveide (līdz 2027. gadam – 74 elektroautobusi), izpildot Transporta enerģijas likuma prasības. Pasākumam būtu jānodrošina 63 500 MWh enerģijas ietaupījums, 34 900 MWh AER un 28 200 tCO₂ samazinājums gadā.</t>
@@ -8036,7 +8057,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aprakstītas AS “Sadales tīkls” investīcijas; pašvaldības izvērtējums nav minēts – jāprecizē.</t>
+          <t>Aprakstītas AS “Sadales tīkls” investīcijas; pašvaldības izvērtējums pārskatā nav aprakstīts.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -8053,11 +8074,7 @@
           <t>4002, 4003</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Plānā paredzēts izvērtēt ETL skaita pieauguma tendences (2030. gadā Latvijā prognozēti 18–60 tūkst. ETL), lai plānotu elektroenerģijas slodzes izmaiņas, uzlādes punktu skaitu un izvietojumu. Pasākumam nav paredzēts tiešs enerģijas ietaupījums un CO₂ emisiju samazinājums.</t>
@@ -8102,11 +8119,7 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Plānā paredzēts, balstoties uz 2021. gadā veikto izpēti, attīstīt zemu emisiju ūdenstransportu kā papildu pārvietošanās veidu. Pasākumam nav paredzēts tiešs enerģijas ietaupījums un CO₂ emisiju samazinājums.</t>
@@ -8168,7 +8181,8 @@
       <c r="O46" t="inlineStr">
         <is>
           <t>Mobilitātes paradumi tiek apzināti aptaujās. NetZeroCities pilotprojektā SEED un iniciatīvā “Elpo Rīga”, kas noslēdzās 2026. gada aprīlī, veikts pētījums par mobilitātes paradumiem; iedzīvotāju mobilitātes aptaujas veic arī CSP.
-Rīgas plānošanas reģions Interreg Centrālbaltijas projektā SuRuMo, izmantojot mobilo operatoru datus, izstrādā rīku iedzīvotāju pārvietošanās paradumu kartēšanai, ko plānots ieviest 2026. gada beigās.</t>
+Rīgas plānošanas reģions Interreg Centrālbaltijas projektā SuRuMo, izmantojot mobilo operatoru datus, izstrādā rīku iedzīvotāju pārvietošanās paradumu kartēšanai, ko plānots ieviest 2026. gada beigās.
+2025. gada septembrī PAD sabiedriskā transporta maršrutu tīkla reformas pētījumā veikta iedzīvotāju aptauja (Kantar, n = 2500, Rīga un pierobežas pašvaldības), un pētījumā analizēti arī e-talonu validāciju un GTFS dati. Aptauja raksturo pārvietošanās veidu izmantošanas biežumu, bet ne braucienu sadalījumu, tāpēc privāto automašīnu lietotāju īpatsvara mērķa monitoringam joprojām nepieciešama regulāra, braucienos balstīta mobilitātes aptauja.</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8209,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dati tiek uzkrāti LVC un ĀMD sistēmās; viedā skaitīšanas sistēma nav minēta.</t>
+          <t>Dati tiek uzkrāti LVC un ĀMD sistēmās; viedās skaitīšanas sistēma pārskatā nav aprakstīta.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -8209,11 +8223,7 @@
           <t>4001</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Plānā paredzēts izveidot viedās sistēmas regulārai automātiskai transportlīdzekļu (automašīnu, autobusu, kravas automašīnu, velosipēdu) uzskaitei, izmantojot projektā SUMBA noteiktos skaitīšanas punktus. Pasākumam nav paredzēts tiešs enerģijas ietaupījums un CO₂ emisiju samazinājums.</t>
@@ -8258,11 +8268,7 @@
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Papildināt</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Plānā paredzēts attīstīt modelēšanas rīkus nākotnes scenāriju veidošanai un analīzei, lai pamatotu pārvaldības un politikas lēmumus. Pasākumam nav paredzēts tiešs enerģijas ietaupījums un CO₂ emisiju samazinājums.</t>
